--- a/morpg/morpg/Assets/TableData/Table_Job.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Job.xlsx
@@ -19,90 +19,81 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="28">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="25">
+  <x:si>
+    <x:t>Alchemist</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Summoner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DemonMage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HiddenEnum</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
   <x:si>
     <x:t>Archmage</x:t>
   </x:si>
   <x:si>
-    <x:t>Required</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HiddenEnum</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SpeciesEnum</x:t>
+    <x:t>Necromancer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DemonFighter</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>notEmployed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Assassin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JobEnum</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rogue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Priest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Default</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Consume</x:t>
   </x:si>
   <x:si>
     <x:t>Index</x:t>
   </x:si>
   <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
+    <x:t>Hidden</x:t>
   </x:si>
   <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Job</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hidden</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Demon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kalapok</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Human</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Default</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sandora</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JobEnum</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Assasin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Priest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rogue</x:t>
-  </x:si>
-  <x:si>
     <x:t>Warrior</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Necromancer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Summoner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Alchemist</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -878,45 +869,45 @@
   <x:sheetData>
     <x:row r="1" spans="1:7">
       <x:c r="A1" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F1" s="7"/>
       <x:c r="G1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:7">
       <x:c r="A2" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="C2" s="1" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F2" s="7"/>
       <x:c r="G2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -927,7 +918,7 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -940,17 +931,17 @@
       <x:c r="A5" s="1">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B5" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C5" s="1" t="s">
-        <x:v>22</x:v>
+      <x:c r="B5" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C5" s="2" t="s">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E5" s="1">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="7"/>
       <x:c r="G5" s="1"/>
@@ -959,17 +950,17 @@
       <x:c r="A6" s="2">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B6" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C6" s="1" t="s">
-        <x:v>23</x:v>
+      <x:c r="B6" s="2" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C6" s="2" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E6" s="1">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F6" s="8"/>
     </x:row>
@@ -977,17 +968,17 @@
       <x:c r="A7" s="1">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B7" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C7" s="1" t="s">
-        <x:v>24</x:v>
+      <x:c r="B7" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C7" s="2" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E7" s="1">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F7" s="7"/>
     </x:row>
@@ -995,17 +986,17 @@
       <x:c r="A8" s="2">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B8" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C8" s="1" t="s">
-        <x:v>20</x:v>
+      <x:c r="B8" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E8" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E8" s="1">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F8" s="8"/>
     </x:row>
@@ -1013,17 +1004,17 @@
       <x:c r="A9" s="1">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B9" s="1" t="s">
+      <x:c r="B9" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C9" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C9" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>6</x:v>
+      <x:c r="E9" s="1">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F9" s="7"/>
     </x:row>
@@ -1031,17 +1022,17 @@
       <x:c r="A10" s="2">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B10" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C10" s="1" t="s">
-        <x:v>21</x:v>
+      <x:c r="B10" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C10" s="2" t="s">
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E10" s="1">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F10" s="8"/>
     </x:row>
@@ -1049,17 +1040,17 @@
       <x:c r="A11" s="1">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B11" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>26</x:v>
+      <x:c r="B11" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C11" s="2" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D11" s="2" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E11" s="1">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F11" s="7"/>
     </x:row>
@@ -1067,17 +1058,17 @@
       <x:c r="A12" s="2">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B12" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C12" s="1" t="s">
-        <x:v>27</x:v>
+      <x:c r="B12" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C12" s="2" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D12" s="2" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E12" s="1">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F12" s="8"/>
     </x:row>
@@ -1085,17 +1076,17 @@
       <x:c r="A13" s="1">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B13" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C13" s="1" t="s">
-        <x:v>25</x:v>
+      <x:c r="B13" s="2" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C13" s="2" t="s">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="2" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E13" s="1">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F13" s="7"/>
     </x:row>
@@ -1103,17 +1094,17 @@
       <x:c r="A14" s="2">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B14" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>13</x:v>
+      <x:c r="B14" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C14" s="2" t="s">
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D14" s="2" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E14" s="1">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F14" s="8"/>
     </x:row>
@@ -1121,31 +1112,54 @@
       <x:c r="A15" s="1">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B15" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C15" s="1" t="s">
-        <x:v>0</x:v>
+      <x:c r="B15" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C15" s="2" t="s">
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D15" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E15" s="1">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F15" s="7"/>
+    </x:row>
+    <x:row r="16" spans="1:6">
+      <x:c r="A16">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F15" s="7"/>
-    </x:row>
-    <x:row r="16" spans="2:6">
-      <x:c r="B16" s="1"/>
-      <x:c r="C16" s="1"/>
-      <x:c r="E16" s="3"/>
+      <x:c r="B16" s="2" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C16" s="2" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D16" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E16" s="3">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="F16" s="8"/>
     </x:row>
     <x:row r="17" spans="1:6">
-      <x:c r="A17" s="1"/>
-      <x:c r="B17" s="1"/>
-      <x:c r="C17" s="1"/>
-      <x:c r="E17" s="1"/>
+      <x:c r="A17" s="1">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B17" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C17" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D17" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E17" s="1">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="F17" s="7"/>
     </x:row>
     <x:row r="18" spans="2:6">

--- a/morpg/morpg/Assets/TableData/Table_Job.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Job.xlsx
@@ -21,40 +21,61 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="25">
   <x:si>
+    <x:t>Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DemonFighter</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Assassin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Necromancer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archmage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>notEmployed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DemonMage</x:t>
+  </x:si>
+  <x:si>
     <x:t>Alchemist</x:t>
   </x:si>
   <x:si>
+    <x:t>HiddenEnum</x:t>
+  </x:si>
+  <x:si>
     <x:t>Summoner</x:t>
   </x:si>
   <x:si>
-    <x:t>DemonMage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HiddenEnum</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archmage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Necromancer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DemonFighter</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Job</x:t>
-  </x:si>
-  <x:si>
-    <x:t>notEmployed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Assassin</x:t>
+    <x:t>Default</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Index</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hidden</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Consume</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Warrior</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
   </x:si>
   <x:si>
     <x:t>JobEnum</x:t>
@@ -63,37 +84,16 @@
     <x:t>Archer</x:t>
   </x:si>
   <x:si>
+    <x:t>Rogue</x:t>
+  </x:si>
+  <x:si>
     <x:t>Mage</x:t>
   </x:si>
   <x:si>
-    <x:t>Rogue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
     <x:t>Priest</x:t>
   </x:si>
   <x:si>
     <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Default</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Consume</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Index</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hidden</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Warrior</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -869,45 +869,45 @@
   <x:sheetData>
     <x:row r="1" spans="1:7">
       <x:c r="A1" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F1" s="7"/>
       <x:c r="G1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:7">
       <x:c r="A2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F2" s="7"/>
       <x:c r="G2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -918,7 +918,7 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -932,13 +932,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C5" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E5" s="1">
         <x:v>0</x:v>
@@ -951,13 +951,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C6" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E6" s="1">
         <x:v>0</x:v>
@@ -969,13 +969,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C7" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E7" s="1">
         <x:v>0</x:v>
@@ -987,13 +987,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E8" s="1">
         <x:v>0</x:v>
@@ -1005,13 +1005,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E9" s="1">
         <x:v>0</x:v>
@@ -1023,13 +1023,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C10" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E10" s="1">
         <x:v>0</x:v>
@@ -1041,13 +1041,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C11" s="2" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D11" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E11" s="1">
         <x:v>0</x:v>
@@ -1059,13 +1059,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D12" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E12" s="1">
         <x:v>1</x:v>
@@ -1077,13 +1077,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B13" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D13" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E13" s="1">
         <x:v>1</x:v>
@@ -1095,13 +1095,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B14" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C14" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D14" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E14" s="1">
         <x:v>1</x:v>
@@ -1113,13 +1113,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B15" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C15" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D15" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E15" s="1">
         <x:v>2</x:v>
@@ -1131,13 +1131,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B16" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C16" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D16" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E16" s="3">
         <x:v>2</x:v>
@@ -1155,7 +1155,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D17" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E17" s="1">
         <x:v>3</x:v>

--- a/morpg/morpg/Assets/TableData/Table_Job.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Job.xlsx
@@ -21,13 +21,31 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="25">
   <x:si>
+    <x:t>DemonFighter</x:t>
+  </x:si>
+  <x:si>
     <x:t>Job</x:t>
   </x:si>
   <x:si>
     <x:t>int</x:t>
   </x:si>
   <x:si>
-    <x:t>DemonFighter</x:t>
+    <x:t>Alchemist</x:t>
+  </x:si>
+  <x:si>
+    <x:t>notEmployed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Summoner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HiddenEnum</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archmage</x:t>
   </x:si>
   <x:si>
     <x:t>Assassin</x:t>
@@ -36,64 +54,46 @@
     <x:t>Necromancer</x:t>
   </x:si>
   <x:si>
-    <x:t>Archmage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>notEmployed</x:t>
-  </x:si>
-  <x:si>
     <x:t>DemonMage</x:t>
   </x:si>
   <x:si>
-    <x:t>Alchemist</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HiddenEnum</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Summoner</x:t>
-  </x:si>
-  <x:si>
     <x:t>Default</x:t>
   </x:si>
   <x:si>
+    <x:t>Hidden</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Consume</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rogue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Warrior</x:t>
+  </x:si>
+  <x:si>
     <x:t>Index</x:t>
   </x:si>
   <x:si>
-    <x:t>Hidden</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Consume</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Warrior</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
     <x:t>Array</x:t>
   </x:si>
   <x:si>
+    <x:t>Archer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Priest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
     <x:t>JobEnum</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rogue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Priest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -863,51 +863,52 @@
   <x:cols>
     <x:col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
     <x:col min="2" max="2" width="24.80078125" customWidth="1"/>
+    <x:col min="3" max="3" width="12.75390625" bestFit="1" customWidth="1"/>
     <x:col min="5" max="5" width="8.796875" bestFit="1" customWidth="1"/>
     <x:col min="6" max="6" width="8.796875" style="6" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:7">
       <x:c r="A1" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F1" s="7"/>
       <x:c r="G1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:7">
       <x:c r="A2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
         <x:v>14</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>15</x:v>
       </x:c>
       <x:c r="F2" s="7"/>
       <x:c r="G2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -918,7 +919,7 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -932,10 +933,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C5" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
         <x:v>12</x:v>
@@ -951,10 +952,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>12</x:v>
@@ -987,10 +988,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
         <x:v>12</x:v>
@@ -1005,10 +1006,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
         <x:v>12</x:v>
@@ -1023,10 +1024,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C10" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
         <x:v>12</x:v>
@@ -1041,10 +1042,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C11" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
         <x:v>12</x:v>
@@ -1059,13 +1060,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C12" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D12" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E12" s="1">
         <x:v>1</x:v>
@@ -1077,13 +1078,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B13" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D13" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E13" s="1">
         <x:v>1</x:v>
@@ -1095,13 +1096,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B14" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C14" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D14" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E14" s="1">
         <x:v>1</x:v>
@@ -1113,13 +1114,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B15" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C15" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E15" s="1">
         <x:v>2</x:v>
@@ -1131,13 +1132,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B16" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C16" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D16" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E16" s="3">
         <x:v>2</x:v>
@@ -1149,13 +1150,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B17" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C17" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D17" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E17" s="1">
         <x:v>3</x:v>
